--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -1466,28 +1466,28 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27">
         <v>31</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>8.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="I27" s="2">
         <v>8.4</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1501,19 +1501,19 @@
         <v>45</v>
       </c>
       <c r="D28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>39</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I28" s="2">
         <v>8.6</v>
@@ -1638,28 +1638,28 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E32">
         <v>156</v>
       </c>
       <c r="F32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32" s="1">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H32" s="1">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I32" s="2">
         <v>8.1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1673,13 +1673,13 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -1708,19 +1708,19 @@
         <v>50</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>21</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="H34" s="1">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
@@ -1778,28 +1778,28 @@
         <v>52</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H36" s="1">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="I36" s="2">
         <v>7.1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1880,19 +1880,19 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E39">
         <v>95</v>
       </c>
       <c r="F39">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G39" s="1">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="H39" s="1">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="I39" s="2">
         <v>5.5</v>
@@ -1901,7 +1901,7 @@
         <v>39</v>
       </c>
       <c r="K39" s="1">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1976,13 +1976,13 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E42">
         <v>714</v>
       </c>
       <c r="F42">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G42" s="1">
         <v>69.5</v>
@@ -1994,10 +1994,10 @@
         <v>6.4</v>
       </c>
       <c r="J42">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K42" s="1">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
@@ -2925,13 +2925,13 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -2960,13 +2960,13 @@
         <v>45</v>
       </c>
       <c r="D28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -3097,13 +3097,13 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -3132,13 +3132,13 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -3167,13 +3167,13 @@
         <v>50</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3237,13 +3237,13 @@
         <v>52</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -3339,13 +3339,13 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -3435,13 +3435,13 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -4384,28 +4384,28 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27">
         <v>31</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>8.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="I27" s="2">
         <v>8.4</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4419,19 +4419,19 @@
         <v>45</v>
       </c>
       <c r="D28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>39</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I28" s="2">
         <v>8.6</v>
@@ -4556,28 +4556,28 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E32">
         <v>156</v>
       </c>
       <c r="F32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32" s="1">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H32" s="1">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I32" s="2">
         <v>8.1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4591,13 +4591,13 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -4626,19 +4626,19 @@
         <v>50</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>21</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="H34" s="1">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
@@ -4696,28 +4696,28 @@
         <v>52</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H36" s="1">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="I36" s="2">
         <v>7.1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4798,19 +4798,19 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E39">
         <v>95</v>
       </c>
       <c r="F39">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G39" s="1">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="H39" s="1">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="I39" s="2">
         <v>5.5</v>
@@ -4819,7 +4819,7 @@
         <v>39</v>
       </c>
       <c r="K39" s="1">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4894,13 +4894,13 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E42">
         <v>714</v>
       </c>
       <c r="F42">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G42" s="1">
         <v>69.5</v>
@@ -4912,10 +4912,10 @@
         <v>6.4</v>
       </c>
       <c r="J42">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K42" s="1">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -1297,28 +1297,28 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>8</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="H22" s="1">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="I22" s="2">
         <v>7.3</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1329,28 +1329,28 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E23">
         <v>161</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1">
-        <v>84.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1399,28 +1399,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>31</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1431,28 +1431,28 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E26">
         <v>69</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1976,28 +1976,28 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E42">
         <v>714</v>
       </c>
       <c r="F42">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G42" s="1">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="H42" s="1">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="I42" s="2">
         <v>6.4</v>
       </c>
       <c r="J42">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K42" s="1">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
     </row>
   </sheetData>
@@ -2756,13 +2756,13 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2788,13 +2788,13 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -2858,13 +2858,13 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -2890,13 +2890,13 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -3435,13 +3435,13 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -4215,28 +4215,28 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>8</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="H22" s="1">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="I22" s="2">
         <v>7.3</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4247,28 +4247,28 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E23">
         <v>161</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1">
-        <v>84.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4317,28 +4317,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>31</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4349,28 +4349,28 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E26">
         <v>69</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4894,28 +4894,28 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E42">
         <v>714</v>
       </c>
       <c r="F42">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G42" s="1">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="H42" s="1">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="I42" s="2">
         <v>6.4</v>
       </c>
       <c r="J42">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K42" s="1">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -641,19 +641,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
       <c r="H3" s="1">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I7" s="2">
         <v>8.199999999999999</v>
@@ -810,22 +810,22 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="H8" s="1">
-        <v>18.3</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -848,25 +848,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -880,28 +880,28 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -918,25 +918,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -953,25 +953,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -988,25 +988,25 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1052,28 +1052,28 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="F15">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1">
-        <v>16.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>83.3</v>
+        <v>12.9</v>
       </c>
       <c r="I15" s="2">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>83.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1227,28 +1227,28 @@
         <v>39</v>
       </c>
       <c r="D20">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>33</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>94.3</v>
+        <v>91.7</v>
       </c>
       <c r="H20" s="1">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I20" s="2">
         <v>8.6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1329,28 +1329,28 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23">
         <v>161</v>
       </c>
       <c r="F23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" s="1">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H23" s="1">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1466,28 +1466,28 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27">
         <v>31</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>88.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H27" s="1">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" s="2">
         <v>8.4</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1638,28 +1638,28 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32">
         <v>156</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
-        <v>92.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I32" s="2">
         <v>8.1</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1673,28 +1673,28 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J33">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1880,28 +1880,28 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F39">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G39" s="1">
-        <v>50.8</v>
+        <v>62.8</v>
       </c>
       <c r="H39" s="1">
-        <v>49.2</v>
+        <v>37.2</v>
       </c>
       <c r="I39" s="2">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>20.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1976,28 +1976,28 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E42">
-        <v>714</v>
+        <v>848</v>
       </c>
       <c r="F42">
-        <v>310</v>
+        <v>177</v>
       </c>
       <c r="G42" s="1">
-        <v>69.7</v>
+        <v>82.7</v>
       </c>
       <c r="H42" s="1">
-        <v>30.3</v>
+        <v>17.3</v>
       </c>
       <c r="I42" s="2">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="J42">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2065,25 +2065,25 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2100,25 +2100,25 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2135,25 +2135,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2170,25 +2170,25 @@
         <v>43</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>69.8</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>30.2</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2205,25 +2205,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2237,28 +2237,28 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2269,28 +2269,28 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F8">
-        <v>219</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>13.6</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2307,25 +2307,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2339,28 +2339,28 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2377,25 +2377,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>23.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2412,25 +2412,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2447,25 +2447,25 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>68.8</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>31.2</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2482,25 +2482,25 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2511,28 +2511,28 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F15">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>26.5</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2686,13 +2686,13 @@
         <v>39</v>
       </c>
       <c r="D20">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -2788,13 +2788,13 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -2826,25 +2826,25 @@
         <v>38</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F24">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J24">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2861,25 +2861,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J25">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2893,25 +2893,25 @@
         <v>69</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F26">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J26">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2925,28 +2925,28 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2963,25 +2963,25 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2998,25 +2998,25 @@
         <v>39</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J29">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3033,25 +3033,25 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3068,25 +3068,25 @@
         <v>25</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3097,28 +3097,28 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F32">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3132,13 +3132,13 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -3339,13 +3339,13 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -3377,25 +3377,25 @@
         <v>36</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J40">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3409,25 +3409,25 @@
         <v>36</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3435,28 +3435,28 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="F42">
-        <v>1024</v>
+        <v>467</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>54.4</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>45.6</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J42">
-        <v>1024</v>
+        <v>402</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>39.2</v>
       </c>
     </row>
   </sheetData>
@@ -3524,19 +3524,19 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
       <c r="H3" s="1">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>13.9</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3629,19 +3629,19 @@
         <v>43</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1">
-        <v>72.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="H5" s="1">
-        <v>27.9</v>
+        <v>30.2</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3664,19 +3664,19 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>59.4</v>
+        <v>93.8</v>
       </c>
       <c r="H6" s="1">
-        <v>40.6</v>
+        <v>6.2</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3696,22 +3696,22 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="I7" s="2">
         <v>8.1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3728,22 +3728,22 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E8">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>81.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3766,25 +3766,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3798,28 +3798,28 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>13.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3836,25 +3836,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>23.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3871,25 +3871,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3906,25 +3906,25 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3970,28 +3970,28 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="G15" s="1">
-        <v>16.7</v>
+        <v>86.5</v>
       </c>
       <c r="H15" s="1">
-        <v>83.3</v>
+        <v>13.5</v>
       </c>
       <c r="I15" s="2">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>83.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4145,28 +4145,28 @@
         <v>39</v>
       </c>
       <c r="D20">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>33</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>94.3</v>
+        <v>91.7</v>
       </c>
       <c r="H20" s="1">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I20" s="2">
         <v>8.6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4247,28 +4247,28 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23">
         <v>161</v>
       </c>
       <c r="F23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" s="1">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H23" s="1">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         <v>44</v>
       </c>
       <c r="D27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27">
         <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H27" s="1">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="I27" s="2">
         <v>8.4</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4422,19 +4422,19 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4457,19 +4457,19 @@
         <v>39</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4492,19 +4492,19 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>16</v>
       </c>
       <c r="I31" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4556,28 +4556,28 @@
         <v>19</v>
       </c>
       <c r="D32">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>92.3</v>
+        <v>94</v>
       </c>
       <c r="H32" s="1">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="I32" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4591,28 +4591,28 @@
         <v>49</v>
       </c>
       <c r="D33">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J33">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4798,28 +4798,28 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F39">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G39" s="1">
-        <v>50.8</v>
+        <v>62.8</v>
       </c>
       <c r="H39" s="1">
-        <v>49.2</v>
+        <v>37.2</v>
       </c>
       <c r="I39" s="2">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>20.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4836,19 +4836,19 @@
         <v>36</v>
       </c>
       <c r="E40">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G40" s="1">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="H40" s="1">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="I40" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4868,19 +4868,19 @@
         <v>36</v>
       </c>
       <c r="E41">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="H41" s="1">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="I41" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4894,28 +4894,28 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E42">
-        <v>714</v>
+        <v>857</v>
       </c>
       <c r="F42">
-        <v>310</v>
+        <v>168</v>
       </c>
       <c r="G42" s="1">
-        <v>69.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>30.3</v>
+        <v>16.4</v>
       </c>
       <c r="I42" s="2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J42">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -1230,25 +1230,25 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I20" s="2">
         <v>8.6</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1332,25 +1332,25 @@
         <v>189</v>
       </c>
       <c r="E23">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1">
-        <v>85.2</v>
+        <v>85.7</v>
       </c>
       <c r="H23" s="1">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1793,13 +1793,13 @@
         <v>26.3</v>
       </c>
       <c r="I36" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1895,13 +1895,13 @@
         <v>37.2</v>
       </c>
       <c r="I39" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1979,25 +1979,25 @@
         <v>1025</v>
       </c>
       <c r="E42">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F42">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G42" s="1">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="H42" s="1">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2549,25 +2549,25 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2584,25 +2584,25 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2654,25 +2654,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2689,25 +2689,25 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2724,25 +2724,25 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>15.2</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2759,25 +2759,25 @@
         <v>12</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2791,25 +2791,25 @@
         <v>189</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3135,25 +3135,25 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3170,25 +3170,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J34">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3205,25 +3205,25 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J35">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3240,25 +3240,25 @@
         <v>19</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J36">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3275,25 +3275,25 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>29.2</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3310,25 +3310,25 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3342,25 +3342,25 @@
         <v>188</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F39">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>44.1</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3438,25 +3438,25 @@
         <v>1025</v>
       </c>
       <c r="E42">
-        <v>558</v>
+        <v>827</v>
       </c>
       <c r="F42">
-        <v>467</v>
+        <v>198</v>
       </c>
       <c r="G42" s="1">
-        <v>54.4</v>
+        <v>80.7</v>
       </c>
       <c r="H42" s="1">
-        <v>45.6</v>
+        <v>19.3</v>
       </c>
       <c r="I42" s="2">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
-        <v>402</v>
+        <v>25</v>
       </c>
       <c r="K42" s="1">
-        <v>39.2</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -4008,19 +4008,19 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H16" s="1">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4043,19 +4043,19 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H17" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I17" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>3.3</v>
       </c>
       <c r="I18" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4113,19 +4113,19 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="H19" s="1">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4160,13 +4160,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4183,19 +4183,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>72.7</v>
+        <v>84.8</v>
       </c>
       <c r="H21" s="1">
-        <v>27.3</v>
+        <v>15.2</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4218,19 +4218,19 @@
         <v>12</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I22" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4250,25 +4250,25 @@
         <v>189</v>
       </c>
       <c r="E23">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1">
-        <v>85.2</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="1">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="I23" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4594,19 +4594,19 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="H33" s="1">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="I33" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4629,19 +4629,19 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G34" s="1">
-        <v>53.8</v>
+        <v>35.9</v>
       </c>
       <c r="H34" s="1">
-        <v>46.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I34" s="2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4664,19 +4664,19 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
       <c r="H35" s="1">
-        <v>64.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I35" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4699,25 +4699,25 @@
         <v>19</v>
       </c>
       <c r="E36">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>73.7</v>
+        <v>47.4</v>
       </c>
       <c r="H36" s="1">
-        <v>26.3</v>
+        <v>52.6</v>
       </c>
       <c r="I36" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4734,19 +4734,19 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1">
-        <v>79.2</v>
+        <v>70.8</v>
       </c>
       <c r="H37" s="1">
-        <v>20.8</v>
+        <v>29.2</v>
       </c>
       <c r="I37" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>6.7</v>
       </c>
       <c r="I38" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4801,25 +4801,25 @@
         <v>188</v>
       </c>
       <c r="E39">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F39">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G39" s="1">
-        <v>62.8</v>
+        <v>55.9</v>
       </c>
       <c r="H39" s="1">
-        <v>37.2</v>
+        <v>44.1</v>
       </c>
       <c r="I39" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4897,25 +4897,25 @@
         <v>1025</v>
       </c>
       <c r="E42">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="F42">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G42" s="1">
-        <v>83.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="I42" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -2342,25 +2342,25 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>33.3</v>
+        <v>72.2</v>
       </c>
       <c r="H10" s="1">
-        <v>66.7</v>
+        <v>27.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J10">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2459,13 +2459,13 @@
         <v>31.2</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2514,25 +2514,25 @@
         <v>155</v>
       </c>
       <c r="E15">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1">
-        <v>73.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>26.5</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3438,25 +3438,25 @@
         <v>1025</v>
       </c>
       <c r="E42">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="F42">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="G42" s="1">
-        <v>80.7</v>
+        <v>82</v>
       </c>
       <c r="H42" s="1">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="I42" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J42">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3801,19 +3801,19 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>86.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="H10" s="1">
-        <v>13.9</v>
+        <v>27.8</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3906,16 +3906,16 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="I13" s="2">
         <v>7.3</v>
@@ -3973,16 +3973,16 @@
         <v>155</v>
       </c>
       <c r="E15">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1">
-        <v>86.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="2">
         <v>7.5</v>
@@ -4897,16 +4897,16 @@
         <v>1025</v>
       </c>
       <c r="E42">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="F42">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G42" s="1">
-        <v>82.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="H42" s="1">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -1297,22 +1297,22 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="H22" s="1">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="I22" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1329,19 +1329,19 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F23">
         <v>27</v>
       </c>
       <c r="G23" s="1">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="H23" s="1">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
@@ -1976,10 +1976,10 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E42">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F42">
         <v>176</v>
@@ -1991,7 +1991,7 @@
         <v>17.2</v>
       </c>
       <c r="I42" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2756,22 +2756,22 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2788,10 +2788,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F23">
         <v>25</v>
@@ -2803,7 +2803,7 @@
         <v>13.2</v>
       </c>
       <c r="I23" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3435,19 +3435,19 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E42">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F42">
         <v>184</v>
       </c>
       <c r="G42" s="1">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I42" s="2">
         <v>7.5</v>
@@ -4215,22 +4215,22 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I22" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4247,10 +4247,10 @@
         <v>19</v>
       </c>
       <c r="D23">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F23">
         <v>25</v>
@@ -4262,7 +4262,7 @@
         <v>13.2</v>
       </c>
       <c r="I23" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4894,19 +4894,19 @@
         <v>22</v>
       </c>
       <c r="D42">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E42">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F42">
         <v>184</v>
       </c>
       <c r="G42" s="1">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -3524,19 +3524,19 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3559,16 +3559,16 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>2.4</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
@@ -3594,19 +3594,19 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3629,16 +3629,16 @@
         <v>43</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>69.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>30.2</v>
+        <v>20.9</v>
       </c>
       <c r="I5" s="2">
         <v>7.2</v>
@@ -3664,19 +3664,19 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3699,19 +3699,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>92.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3731,19 +3731,19 @@
         <v>220</v>
       </c>
       <c r="E8">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="H8" s="1">
-        <v>13.6</v>
+        <v>6.8</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3766,19 +3766,19 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3801,16 +3801,16 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>72.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>27.8</v>
+        <v>13.9</v>
       </c>
       <c r="I10" s="2">
         <v>7</v>
@@ -3836,19 +3836,19 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>76.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H11" s="1">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3906,19 +3906,19 @@
         <v>16</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3973,19 +3973,19 @@
         <v>155</v>
       </c>
       <c r="E15">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F15">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
-        <v>82.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H15" s="1">
-        <v>17.4</v>
+        <v>7.7</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4008,19 +4008,19 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>96.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>3.7</v>
+        <v>11.1</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4043,16 +4043,16 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H17" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I17" s="2">
         <v>7.6</v>
@@ -4078,19 +4078,19 @@
         <v>30</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4113,19 +4113,19 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>77.8</v>
+        <v>96.3</v>
       </c>
       <c r="H19" s="1">
-        <v>22.2</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4148,19 +4148,19 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4183,19 +4183,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="I21" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4218,16 +4218,16 @@
         <v>13</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>76.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H22" s="1">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="I22" s="2">
         <v>7.8</v>
@@ -4250,16 +4250,16 @@
         <v>190</v>
       </c>
       <c r="E23">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>86.8</v>
+        <v>93.7</v>
       </c>
       <c r="H23" s="1">
-        <v>13.2</v>
+        <v>6.3</v>
       </c>
       <c r="I23" s="2">
         <v>8.1</v>
@@ -4387,19 +4387,19 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>40</v>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I28" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4469,7 +4469,7 @@
         <v>5.1</v>
       </c>
       <c r="I29" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4492,19 +4492,19 @@
         <v>30</v>
       </c>
       <c r="E30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I30" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4527,16 +4527,16 @@
         <v>25</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>96</v>
+      </c>
+      <c r="H31" s="1">
         <v>4</v>
-      </c>
-      <c r="G31" s="1">
-        <v>84</v>
-      </c>
-      <c r="H31" s="1">
-        <v>16</v>
       </c>
       <c r="I31" s="2">
         <v>8</v>
@@ -4559,19 +4559,19 @@
         <v>168</v>
       </c>
       <c r="E32">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>94</v>
+        <v>95.8</v>
       </c>
       <c r="H32" s="1">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="I32" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4836,19 +4836,19 @@
         <v>36</v>
       </c>
       <c r="E40">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G40" s="1">
-        <v>75</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H40" s="1">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="I40" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4868,19 +4868,19 @@
         <v>36</v>
       </c>
       <c r="E41">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G41" s="1">
-        <v>75</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="I41" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4897,16 +4897,16 @@
         <v>1026</v>
       </c>
       <c r="E42">
-        <v>842</v>
+        <v>886</v>
       </c>
       <c r="F42">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="G42" s="1">
-        <v>82.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>17.9</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -3322,7 +3322,7 @@
         <v>6.7</v>
       </c>
       <c r="I38" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3836,16 +3836,16 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H11" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I11" s="2">
         <v>7.8</v>
@@ -3973,16 +3973,16 @@
         <v>155</v>
       </c>
       <c r="E15">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1">
-        <v>92.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I15" s="2">
         <v>7.4</v>
@@ -4897,16 +4897,16 @@
         <v>1026</v>
       </c>
       <c r="E42">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F42">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G42" s="1">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H42" s="1">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -4594,19 +4594,19 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>56.4</v>
+        <v>87.2</v>
       </c>
       <c r="H33" s="1">
-        <v>43.6</v>
+        <v>12.8</v>
       </c>
       <c r="I33" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4629,19 +4629,19 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F34">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>35.9</v>
+        <v>79.5</v>
       </c>
       <c r="H34" s="1">
-        <v>64.09999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="I34" s="2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4664,19 +4664,19 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1">
-        <v>40.5</v>
+        <v>83.8</v>
       </c>
       <c r="H35" s="1">
-        <v>59.5</v>
+        <v>16.2</v>
       </c>
       <c r="I35" s="2">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4699,19 +4699,19 @@
         <v>19</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G36" s="1">
-        <v>47.4</v>
+        <v>84.2</v>
       </c>
       <c r="H36" s="1">
-        <v>52.6</v>
+        <v>15.8</v>
       </c>
       <c r="I36" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4734,19 +4734,19 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="1">
-        <v>70.8</v>
+        <v>91.7</v>
       </c>
       <c r="H37" s="1">
-        <v>29.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I37" s="2">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4769,19 +4769,19 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4801,19 +4801,19 @@
         <v>188</v>
       </c>
       <c r="E39">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="F39">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="G39" s="1">
-        <v>55.9</v>
+        <v>87.2</v>
       </c>
       <c r="H39" s="1">
-        <v>44.1</v>
+        <v>12.8</v>
       </c>
       <c r="I39" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4897,19 +4897,19 @@
         <v>1026</v>
       </c>
       <c r="E42">
-        <v>887</v>
+        <v>946</v>
       </c>
       <c r="F42">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="G42" s="1">
-        <v>86.5</v>
+        <v>92.2</v>
       </c>
       <c r="H42" s="1">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="I42" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J42">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>2.4</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>11.1</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>20.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>6.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>13.9</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>3.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>7.1</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>11.1</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>12.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>3.7</v>
       </c>
       <c r="I19" s="2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>12.1</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>7.7</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>6.3</v>
       </c>
       <c r="I23" s="2">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>5.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>2.5</v>
       </c>
       <c r="I28" s="2">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4469,7 +4469,7 @@
         <v>5.1</v>
       </c>
       <c r="I29" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>3.3</v>
       </c>
       <c r="I30" s="2">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>4</v>
       </c>
       <c r="I31" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>4.2</v>
       </c>
       <c r="I32" s="2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4606,7 +4606,7 @@
         <v>12.8</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>20.5</v>
       </c>
       <c r="I34" s="2">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>16.2</v>
       </c>
       <c r="I35" s="2">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4711,7 +4711,7 @@
         <v>15.8</v>
       </c>
       <c r="I36" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4746,7 +4746,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I37" s="2">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>12.8</v>
       </c>
       <c r="I39" s="2">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         <v>30.6</v>
       </c>
       <c r="I40" s="2">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>30.6</v>
       </c>
       <c r="I41" s="2">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4909,7 +4909,7 @@
         <v>7.8</v>
       </c>
       <c r="I42" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J42">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20231.xlsx
+++ b/academias/Inglés - Estadisticos 20231.xlsx
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>2.4</v>
       </c>
       <c r="I3" s="2">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3606,7 +3606,7 @@
         <v>11.1</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>20.9</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>6.8</v>
       </c>
       <c r="I8" s="2">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>13.9</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>3.8</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3985,7 +3985,7 @@
         <v>7.1</v>
       </c>
       <c r="I15" s="2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>11.1</v>
       </c>
       <c r="I16" s="2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>12.5</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>3.7</v>
       </c>
       <c r="I19" s="2">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>12.1</v>
       </c>
       <c r="I21" s="2">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>7.7</v>
       </c>
       <c r="I22" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>6.3</v>
       </c>
       <c r="I23" s="2">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>5.9</v>
       </c>
       <c r="I27" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>2.5</v>
       </c>
       <c r="I28" s="2">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4469,7 +4469,7 @@
         <v>5.1</v>
       </c>
       <c r="I29" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>3.3</v>
       </c>
       <c r="I30" s="2">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>4</v>
       </c>
       <c r="I31" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>4.2</v>
       </c>
       <c r="I32" s="2">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4606,7 +4606,7 @@
         <v>12.8</v>
       </c>
       <c r="I33" s="2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>20.5</v>
       </c>
       <c r="I34" s="2">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>16.2</v>
       </c>
       <c r="I35" s="2">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4711,7 +4711,7 @@
         <v>15.8</v>
       </c>
       <c r="I36" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4746,7 +4746,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I37" s="2">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>12.8</v>
       </c>
       <c r="I39" s="2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         <v>30.6</v>
       </c>
       <c r="I40" s="2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>30.6</v>
       </c>
       <c r="I41" s="2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4909,7 +4909,7 @@
         <v>7.8</v>
       </c>
       <c r="I42" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J42">
         <v>0</v>
